--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59221-2022 artfynd.xlsx
+++ b/artfynd/A 59221-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131471656</v>
       </c>
       <c r="B2" t="n">
-        <v>57102</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131470806</v>
       </c>
       <c r="B3" t="n">
-        <v>58073</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
